--- a/Vignettes/ClimateHCRs/HCR_par.xlsx
+++ b/Vignettes/ClimateHCRs/HCR_par.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/KKH/Documents/GitHub_mac/ACLIM2/Vignettes/ClimateHCRs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30845104-7A94-CB4A-81F0-5C4B1B2D6653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A7A21F-230A-9C4F-A643-C7E9352341FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6520" yWindow="1840" windowWidth="28040" windowHeight="17440" xr2:uid="{29601B6F-7A1C-B44B-9D68-D49A773C8A09}"/>
+    <workbookView xWindow="2740" yWindow="1700" windowWidth="28040" windowHeight="17440" xr2:uid="{29601B6F-7A1C-B44B-9D68-D49A773C8A09}"/>
   </bookViews>
   <sheets>
     <sheet name="HCR_par" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="43">
   <si>
     <t>hcr_cov</t>
   </si>
@@ -159,6 +159,15 @@
   </si>
   <si>
     <t>HCR8b: log_theta set to 0.75 + SSL</t>
+  </si>
+  <si>
+    <t>HCR10a: no offset + SSL</t>
+  </si>
+  <si>
+    <t>HCR10b: small offset + SSL</t>
+  </si>
+  <si>
+    <t>HCR10c: large offset + SSL</t>
   </si>
 </sst>
 </file>
@@ -568,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74F74268-41DB-CD48-95D4-E5979CCBD865}">
-  <dimension ref="A1:G210"/>
+  <dimension ref="A1:G243"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -1363,14 +1372,14 @@
       <c r="A35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="C35" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="D35" s="3">
-        <v>0.05</v>
+      <c r="B35">
+        <v>0.3</v>
+      </c>
+      <c r="C35">
+        <v>0.3</v>
+      </c>
+      <c r="D35">
+        <v>0.3</v>
       </c>
       <c r="E35" s="3">
         <v>2</v>
@@ -2951,13 +2960,16 @@
         <v>38</v>
       </c>
       <c r="B104">
-        <v>-0.5</v>
+        <f>LN(0.1)</f>
+        <v>-2.3025850929940455</v>
       </c>
       <c r="C104">
-        <v>-0.5</v>
+        <f>LN(0.1)</f>
+        <v>-2.3025850929940455</v>
       </c>
       <c r="D104">
-        <v>-0.5</v>
+        <f>LN(0.1)</f>
+        <v>-2.3025850929940455</v>
       </c>
       <c r="E104">
         <v>5</v>
@@ -3204,13 +3216,16 @@
         <v>38</v>
       </c>
       <c r="B115">
-        <v>0.5</v>
+        <f>LN(0.2)</f>
+        <v>-1.6094379124341003</v>
       </c>
       <c r="C115">
-        <v>0.5</v>
+        <f t="shared" ref="C115:D115" si="0">LN(0.2)</f>
+        <v>-1.6094379124341003</v>
       </c>
       <c r="D115">
-        <v>0.5</v>
+        <f t="shared" si="0"/>
+        <v>-1.6094379124341003</v>
       </c>
       <c r="E115">
         <v>5</v>
@@ -3710,13 +3725,16 @@
         <v>38</v>
       </c>
       <c r="B137">
-        <v>-0.5</v>
+        <f>LN(0.1)</f>
+        <v>-2.3025850929940455</v>
       </c>
       <c r="C137">
-        <v>-0.5</v>
+        <f>LN(0.1)</f>
+        <v>-2.3025850929940455</v>
       </c>
       <c r="D137">
-        <v>-0.5</v>
+        <f>LN(0.1)</f>
+        <v>-2.3025850929940455</v>
       </c>
       <c r="E137">
         <v>6</v>
@@ -3963,13 +3981,16 @@
         <v>38</v>
       </c>
       <c r="B148">
-        <v>0.5</v>
+        <f>LN(0.2)</f>
+        <v>-1.6094379124341003</v>
       </c>
       <c r="C148">
-        <v>0.5</v>
+        <f>LN(0.2)</f>
+        <v>-1.6094379124341003</v>
       </c>
       <c r="D148">
-        <v>0.5</v>
+        <f>LN(0.2)</f>
+        <v>-1.6094379124341003</v>
       </c>
       <c r="E148">
         <v>6</v>
@@ -5408,6 +5429,771 @@
       </c>
       <c r="G210" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A211" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B211" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C211" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="D211" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="E211">
+        <v>10</v>
+      </c>
+      <c r="F211" t="s">
+        <v>18</v>
+      </c>
+      <c r="G211" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>7</v>
+      </c>
+      <c r="B212">
+        <v>0.05</v>
+      </c>
+      <c r="C212">
+        <v>0.05</v>
+      </c>
+      <c r="D212">
+        <v>0.05</v>
+      </c>
+      <c r="E212">
+        <v>10</v>
+      </c>
+      <c r="F212" t="s">
+        <v>18</v>
+      </c>
+      <c r="G212" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>6</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="E213">
+        <v>10</v>
+      </c>
+      <c r="F213" t="s">
+        <v>18</v>
+      </c>
+      <c r="G213" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>38</v>
+      </c>
+      <c r="B214" s="5">
+        <v>-1000000000</v>
+      </c>
+      <c r="C214" s="5">
+        <v>-1000000000</v>
+      </c>
+      <c r="D214" s="5">
+        <v>-1000000000</v>
+      </c>
+      <c r="E214">
+        <v>10</v>
+      </c>
+      <c r="F214" t="s">
+        <v>18</v>
+      </c>
+      <c r="G214" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A215" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>0</v>
+      </c>
+      <c r="E215">
+        <v>10</v>
+      </c>
+      <c r="F215" t="s">
+        <v>18</v>
+      </c>
+      <c r="G215" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>36</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="E216">
+        <v>10</v>
+      </c>
+      <c r="F216" t="s">
+        <v>18</v>
+      </c>
+      <c r="G216" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>37</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>0</v>
+      </c>
+      <c r="E217">
+        <v>10</v>
+      </c>
+      <c r="F217" t="s">
+        <v>18</v>
+      </c>
+      <c r="G217" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>4</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+      <c r="E218">
+        <v>10</v>
+      </c>
+      <c r="F218" t="s">
+        <v>18</v>
+      </c>
+      <c r="G218" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>2</v>
+      </c>
+      <c r="B219">
+        <v>0.2</v>
+      </c>
+      <c r="C219">
+        <v>0.2</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219">
+        <v>10</v>
+      </c>
+      <c r="F219" t="s">
+        <v>18</v>
+      </c>
+      <c r="G219" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>1</v>
+      </c>
+      <c r="B220">
+        <v>0.4</v>
+      </c>
+      <c r="C220">
+        <v>0.4</v>
+      </c>
+      <c r="D220">
+        <v>0.4</v>
+      </c>
+      <c r="E220">
+        <v>10</v>
+      </c>
+      <c r="F220" t="s">
+        <v>18</v>
+      </c>
+      <c r="G220" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>0</v>
+      </c>
+      <c r="B221">
+        <v>6</v>
+      </c>
+      <c r="C221">
+        <v>6</v>
+      </c>
+      <c r="D221">
+        <v>6</v>
+      </c>
+      <c r="E221">
+        <v>10</v>
+      </c>
+      <c r="F221" t="s">
+        <v>18</v>
+      </c>
+      <c r="G221" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A222" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B222" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C222" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="D222" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="E222">
+        <v>10</v>
+      </c>
+      <c r="F222" t="s">
+        <v>16</v>
+      </c>
+      <c r="G222" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>7</v>
+      </c>
+      <c r="B223">
+        <v>0.05</v>
+      </c>
+      <c r="C223">
+        <v>0.05</v>
+      </c>
+      <c r="D223">
+        <v>0.05</v>
+      </c>
+      <c r="E223">
+        <v>10</v>
+      </c>
+      <c r="F223" t="s">
+        <v>16</v>
+      </c>
+      <c r="G223" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>6</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224">
+        <v>0</v>
+      </c>
+      <c r="E224">
+        <v>10</v>
+      </c>
+      <c r="F224" t="s">
+        <v>16</v>
+      </c>
+      <c r="G224" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>38</v>
+      </c>
+      <c r="B225">
+        <f>LN(0.25)</f>
+        <v>-1.3862943611198906</v>
+      </c>
+      <c r="C225">
+        <f>LN(0.25)</f>
+        <v>-1.3862943611198906</v>
+      </c>
+      <c r="D225">
+        <f>LN(0.25)</f>
+        <v>-1.3862943611198906</v>
+      </c>
+      <c r="E225">
+        <v>10</v>
+      </c>
+      <c r="F225" t="s">
+        <v>16</v>
+      </c>
+      <c r="G225" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A226" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <v>0</v>
+      </c>
+      <c r="E226">
+        <v>10</v>
+      </c>
+      <c r="F226" t="s">
+        <v>16</v>
+      </c>
+      <c r="G226" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>36</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>0</v>
+      </c>
+      <c r="E227">
+        <v>10</v>
+      </c>
+      <c r="F227" t="s">
+        <v>16</v>
+      </c>
+      <c r="G227" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>37</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>10</v>
+      </c>
+      <c r="F228" t="s">
+        <v>16</v>
+      </c>
+      <c r="G228" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>4</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>0</v>
+      </c>
+      <c r="E229">
+        <v>10</v>
+      </c>
+      <c r="F229" t="s">
+        <v>16</v>
+      </c>
+      <c r="G229" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>2</v>
+      </c>
+      <c r="B230">
+        <v>0.2</v>
+      </c>
+      <c r="C230">
+        <v>0.2</v>
+      </c>
+      <c r="D230">
+        <v>0</v>
+      </c>
+      <c r="E230">
+        <v>10</v>
+      </c>
+      <c r="F230" t="s">
+        <v>16</v>
+      </c>
+      <c r="G230" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>1</v>
+      </c>
+      <c r="B231">
+        <v>0.4</v>
+      </c>
+      <c r="C231">
+        <v>0.4</v>
+      </c>
+      <c r="D231">
+        <v>0.4</v>
+      </c>
+      <c r="E231">
+        <v>10</v>
+      </c>
+      <c r="F231" t="s">
+        <v>16</v>
+      </c>
+      <c r="G231" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>0</v>
+      </c>
+      <c r="B232">
+        <v>6</v>
+      </c>
+      <c r="C232">
+        <v>6</v>
+      </c>
+      <c r="D232">
+        <v>6</v>
+      </c>
+      <c r="E232">
+        <v>10</v>
+      </c>
+      <c r="F232" t="s">
+        <v>16</v>
+      </c>
+      <c r="G232" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A233" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B233" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C233" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="D233" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="E233">
+        <v>10</v>
+      </c>
+      <c r="F233" t="s">
+        <v>21</v>
+      </c>
+      <c r="G233" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>7</v>
+      </c>
+      <c r="B234">
+        <v>0.05</v>
+      </c>
+      <c r="C234">
+        <v>0.05</v>
+      </c>
+      <c r="D234">
+        <v>0.05</v>
+      </c>
+      <c r="E234">
+        <v>10</v>
+      </c>
+      <c r="F234" t="s">
+        <v>21</v>
+      </c>
+      <c r="G234" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>6</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235">
+        <v>0</v>
+      </c>
+      <c r="E235">
+        <v>10</v>
+      </c>
+      <c r="F235" t="s">
+        <v>21</v>
+      </c>
+      <c r="G235" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>38</v>
+      </c>
+      <c r="B236">
+        <f>LN(0.5)</f>
+        <v>-0.69314718055994529</v>
+      </c>
+      <c r="C236">
+        <f>LN(0.5)</f>
+        <v>-0.69314718055994529</v>
+      </c>
+      <c r="D236">
+        <f>LN(0.5)</f>
+        <v>-0.69314718055994529</v>
+      </c>
+      <c r="E236">
+        <v>10</v>
+      </c>
+      <c r="F236" t="s">
+        <v>21</v>
+      </c>
+      <c r="G236" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A237" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>0</v>
+      </c>
+      <c r="E237">
+        <v>10</v>
+      </c>
+      <c r="F237" t="s">
+        <v>21</v>
+      </c>
+      <c r="G237" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>36</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238">
+        <v>0</v>
+      </c>
+      <c r="E238">
+        <v>10</v>
+      </c>
+      <c r="F238" t="s">
+        <v>21</v>
+      </c>
+      <c r="G238" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>37</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+      <c r="D239">
+        <v>0</v>
+      </c>
+      <c r="E239">
+        <v>10</v>
+      </c>
+      <c r="F239" t="s">
+        <v>21</v>
+      </c>
+      <c r="G239" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>4</v>
+      </c>
+      <c r="B240">
+        <v>0</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>0</v>
+      </c>
+      <c r="E240">
+        <v>10</v>
+      </c>
+      <c r="F240" t="s">
+        <v>21</v>
+      </c>
+      <c r="G240" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>2</v>
+      </c>
+      <c r="B241">
+        <v>0.2</v>
+      </c>
+      <c r="C241">
+        <v>0.2</v>
+      </c>
+      <c r="D241">
+        <v>0</v>
+      </c>
+      <c r="E241">
+        <v>10</v>
+      </c>
+      <c r="F241" t="s">
+        <v>21</v>
+      </c>
+      <c r="G241" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>1</v>
+      </c>
+      <c r="B242">
+        <v>0.4</v>
+      </c>
+      <c r="C242">
+        <v>0.4</v>
+      </c>
+      <c r="D242">
+        <v>0.4</v>
+      </c>
+      <c r="E242">
+        <v>10</v>
+      </c>
+      <c r="F242" t="s">
+        <v>21</v>
+      </c>
+      <c r="G242" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>0</v>
+      </c>
+      <c r="B243">
+        <v>6</v>
+      </c>
+      <c r="C243">
+        <v>6</v>
+      </c>
+      <c r="D243">
+        <v>6</v>
+      </c>
+      <c r="E243">
+        <v>10</v>
+      </c>
+      <c r="F243" t="s">
+        <v>21</v>
+      </c>
+      <c r="G243" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Vignettes/ClimateHCRs/HCR_par.xlsx
+++ b/Vignettes/ClimateHCRs/HCR_par.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/KKH/Documents/GitHub_mac/ACLIM2/Vignettes/ClimateHCRs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A7A21F-230A-9C4F-A643-C7E9352341FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB702906-0C1F-9346-A19C-CE1F7C0B28DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2740" yWindow="1700" windowWidth="28040" windowHeight="17440" xr2:uid="{29601B6F-7A1C-B44B-9D68-D49A773C8A09}"/>
+    <workbookView xWindow="3200" yWindow="3160" windowWidth="28040" windowHeight="17440" xr2:uid="{29601B6F-7A1C-B44B-9D68-D49A773C8A09}"/>
   </bookViews>
   <sheets>
     <sheet name="HCR_par" sheetId="2" r:id="rId1"/>
@@ -161,13 +161,13 @@
     <t>HCR8b: log_theta set to 0.75 + SSL</t>
   </si>
   <si>
-    <t>HCR10a: no offset + SSL</t>
+    <t>HCR10c: large offset + SSL</t>
   </si>
   <si>
-    <t>HCR10b: small offset + SSL</t>
+    <t>HCR10b: med offset + SSL</t>
   </si>
   <si>
-    <t>HCR10c: large offset + SSL</t>
+    <t>HCR10a: small offset + SSL</t>
   </si>
 </sst>
 </file>
@@ -5451,7 +5451,7 @@
         <v>18</v>
       </c>
       <c r="G211" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.2">
@@ -5474,7 +5474,7 @@
         <v>18</v>
       </c>
       <c r="G212" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.2">
@@ -5497,21 +5497,24 @@
         <v>18</v>
       </c>
       <c r="G213" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>38</v>
       </c>
-      <c r="B214" s="5">
-        <v>-1000000000</v>
-      </c>
-      <c r="C214" s="5">
-        <v>-1000000000</v>
-      </c>
-      <c r="D214" s="5">
-        <v>-1000000000</v>
+      <c r="B214">
+        <f>LN(0.5)</f>
+        <v>-0.69314718055994529</v>
+      </c>
+      <c r="C214">
+        <f>LN(0.5)</f>
+        <v>-0.69314718055994529</v>
+      </c>
+      <c r="D214">
+        <f>LN(0.5)</f>
+        <v>-0.69314718055994529</v>
       </c>
       <c r="E214">
         <v>10</v>
@@ -5520,7 +5523,7 @@
         <v>18</v>
       </c>
       <c r="G214" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.2">
@@ -5543,7 +5546,7 @@
         <v>18</v>
       </c>
       <c r="G215" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.2">
@@ -5566,7 +5569,7 @@
         <v>18</v>
       </c>
       <c r="G216" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.2">
@@ -5589,7 +5592,7 @@
         <v>18</v>
       </c>
       <c r="G217" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.2">
@@ -5612,7 +5615,7 @@
         <v>18</v>
       </c>
       <c r="G218" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.2">
@@ -5635,7 +5638,7 @@
         <v>18</v>
       </c>
       <c r="G219" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.2">
@@ -5658,7 +5661,7 @@
         <v>18</v>
       </c>
       <c r="G220" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.2">
@@ -5681,7 +5684,7 @@
         <v>18</v>
       </c>
       <c r="G221" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.2">
@@ -5758,16 +5761,16 @@
         <v>38</v>
       </c>
       <c r="B225">
-        <f>LN(0.25)</f>
-        <v>-1.3862943611198906</v>
+        <f>LN(1.5)</f>
+        <v>0.40546510810816438</v>
       </c>
       <c r="C225">
-        <f>LN(0.25)</f>
-        <v>-1.3862943611198906</v>
+        <f>LN(1.5)</f>
+        <v>0.40546510810816438</v>
       </c>
       <c r="D225">
-        <f>LN(0.25)</f>
-        <v>-1.3862943611198906</v>
+        <f>LN(1.5)</f>
+        <v>0.40546510810816438</v>
       </c>
       <c r="E225">
         <v>10</v>
@@ -5960,7 +5963,7 @@
         <v>21</v>
       </c>
       <c r="G233" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
@@ -5983,7 +5986,7 @@
         <v>21</v>
       </c>
       <c r="G234" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.2">
@@ -6006,7 +6009,7 @@
         <v>21</v>
       </c>
       <c r="G235" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
@@ -6014,16 +6017,16 @@
         <v>38</v>
       </c>
       <c r="B236">
-        <f>LN(0.5)</f>
-        <v>-0.69314718055994529</v>
+        <f>LN(3)</f>
+        <v>1.0986122886681098</v>
       </c>
       <c r="C236">
-        <f>LN(0.5)</f>
-        <v>-0.69314718055994529</v>
+        <f t="shared" ref="C236:D236" si="1">LN(3)</f>
+        <v>1.0986122886681098</v>
       </c>
       <c r="D236">
-        <f>LN(0.5)</f>
-        <v>-0.69314718055994529</v>
+        <f t="shared" si="1"/>
+        <v>1.0986122886681098</v>
       </c>
       <c r="E236">
         <v>10</v>
@@ -6032,7 +6035,7 @@
         <v>21</v>
       </c>
       <c r="G236" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
@@ -6055,7 +6058,7 @@
         <v>21</v>
       </c>
       <c r="G237" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
@@ -6078,7 +6081,7 @@
         <v>21</v>
       </c>
       <c r="G238" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
@@ -6101,7 +6104,7 @@
         <v>21</v>
       </c>
       <c r="G239" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
@@ -6124,7 +6127,7 @@
         <v>21</v>
       </c>
       <c r="G240" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.2">
@@ -6147,7 +6150,7 @@
         <v>21</v>
       </c>
       <c r="G241" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.2">
@@ -6170,7 +6173,7 @@
         <v>21</v>
       </c>
       <c r="G242" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.2">
@@ -6193,7 +6196,7 @@
         <v>21</v>
       </c>
       <c r="G243" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
